--- a/demo-files/Kontaktliste.xlsx
+++ b/demo-files/Kontaktliste.xlsx
@@ -7,9 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$E$11</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,8 +28,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <sz val="11"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -39,8 +46,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00F2F4F7"/>
+        <bgColor rgb="00F2F4F7"/>
       </patternFill>
     </fill>
   </fills>
@@ -53,10 +60,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00D0D5DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D5DD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D5DD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D5DD"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -65,10 +80,10 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -435,15 +450,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -459,7 +473,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Rolle</t>
+          <t>Funktion</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -470,87 +484,72 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Telefon</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Mobiltelefon</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Dr. Martin Müller</t>
+          <t>Dr. Stefan Meier</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Müller &amp; Schmidt Immobilien GmbH</t>
+          <t>Seefeld Immobilien AG</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Bauherr</t>
+          <t>Bauherrenvertreter</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>mueller@ms-immo.de</t>
+          <t>s.meier@seefeld-immo.ch</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>089 12345-100</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>0171 111 2233</t>
+          <t>+41 44 380 22 10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Arch. Sabine Lechner</t>
+          <t>Arch. ETH Laura Brunner</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Architekten Lechner &amp; Kollegen</t>
+          <t>Baumschlager Eberle Architekten</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Generalplanerin</t>
+          <t>Projektleiterin GP</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>lechner@arch-lk.de</t>
+          <t>brunner@be-arch.ch</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>089 98765-200</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>0172 222 3344</t>
+          <t>+41 44 561 33 00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Dipl.-Ing. Thomas Berger</t>
+          <t>Dipl. Bauing. ETH Marco Keller</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Berger Baumanagement GmbH</t>
+          <t>Implenia Schweiz AG</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -560,245 +559,206 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>berger@bau-mg.de</t>
+          <t>m.keller@implenia.com</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>089 54321-50</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0171 555 2341</t>
+          <t>+41 58 474 00 00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Ing. Andrea Hofmann</t>
+          <t>Ing. Nina Frei</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Hofmann Sicherheitstechnik</t>
+          <t>SIBE Zürich GmbH</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>SiGeKo</t>
+          <t>Sicherheitsbeauftragte</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>hofmann@sigeko.de</t>
+          <t>n.frei@sibe-zuerich.ch</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>089 77777-10</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0172 888 4567</t>
+          <t>+41 44 720 15 30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Hr. Josef Bauer</t>
+          <t>Roman Steiner</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Bauer Tiefbau GmbH</t>
+          <t>Implenia Schweiz AG</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Erdarbeiten</t>
+          <t>Polier</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>bauer@bauer-tiefbau.de</t>
+          <t>r.steiner@implenia.com</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>089 66666-30</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0170 444 5566</t>
+          <t>+41 79 445 12 88</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Fr. Claudia Kellner</t>
+          <t>Dr. Ing. Thomas Wyss</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Züblin AG, NL München</t>
+          <t>Schnetzer Puskas Ingenieure</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Rohbau</t>
+          <t>Tragwerksplaner</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>kellner@zueblin.de</t>
+          <t>wyss@schnetzer-puskas.ch</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>089 55555-20</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0171 666 7788</t>
+          <t>+41 44 315 77 00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Michael Gruber</t>
+          <t>Markus Roth</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Bauer Tiefbau GmbH</t>
+          <t>Amstein + Walthert AG</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Polier</t>
+          <t>HLKS-Planer</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>gruber@bauer-tiefbau.de</t>
+          <t>roth@amstein-walthert.ch</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0170 333 9876</t>
+          <t>+41 44 305 91 11</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Hr. Werner Weiss</t>
+          <t>Claudia Gerber</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Metallbau Schüco Partner</t>
+          <t>Kanton Zürich, Baupolizei</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Fassade</t>
+          <t>Baubehörde</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>weiss@schueco-partner.de</t>
+          <t>claudia.gerber@bd.zh.ch</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>089 44444-15</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0172 999 0011</t>
+          <t>+41 43 259 30 45</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Hr. Karl Müller</t>
+          <t>Peter Huber</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Elektro Müller GmbH</t>
+          <t>Marti AG Zürich</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Elektro</t>
+          <t>Baumeisterarbeiten</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>k.mueller@elektro-mueller.de</t>
+          <t>p.huber@martiag.ch</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>089 33333-25</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0173 111 2244</t>
+          <t>+41 44 307 80 00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Fr. Petra Wagner</t>
+          <t>Sandra Bieri</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Haustechnik Süd GmbH</t>
+          <t>Ernst Basler + Partner</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>HLKS</t>
+          <t>Umweltberatung</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>wagner@ht-sued.de</t>
+          <t>bieri@ebp.ch</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>089 22222-35</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0174 222 3355</t>
+          <t>+41 44 395 11 11</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>